--- a/xpts_schedule.xlsx
+++ b/xpts_schedule.xlsx
@@ -54027,127 +54027,127 @@
         <v>245</v>
       </c>
       <c r="I344" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J344" t="b">
         <v>0</v>
       </c>
       <c r="K344" t="n">
-        <v>73.02</v>
+        <v>23.98</v>
       </c>
       <c r="L344" t="n">
         <v>0.2142688969421128</v>
       </c>
       <c r="M344" t="n">
-        <v>4.81531509216151</v>
+        <v>2.019290564194488</v>
       </c>
       <c r="N344" t="n">
-        <v>163.7207131334913</v>
+        <v>68.65587918261259</v>
       </c>
       <c r="O344" t="n">
-        <v>36.38238069633141</v>
+        <v>15.25686204058058</v>
       </c>
       <c r="P344" t="n">
-        <v>4.30024871337594</v>
+        <v>1.85014112892637</v>
       </c>
       <c r="Q344" t="n">
-        <v>5.358952942195087</v>
+        <v>2.197822961398065</v>
       </c>
       <c r="R344" t="n">
         <v>0</v>
       </c>
       <c r="S344" t="n">
-        <v>4.861665047729974</v>
+        <v>2.034512036866793</v>
       </c>
       <c r="T344" t="n">
-        <v>9.453696692262202</v>
+        <v>3.980475607441037</v>
       </c>
       <c r="U344" t="n">
-        <v>4.35951250176273</v>
+        <v>1.869603545326194</v>
       </c>
       <c r="V344" t="n">
-        <v>4.008100333194276</v>
+        <v>1.754198672657453</v>
       </c>
       <c r="W344" t="n">
-        <v>5.535720096156643</v>
+        <v>2.255873856385713</v>
       </c>
       <c r="X344" t="n">
-        <v>4.402156821995048</v>
+        <v>1.883608075580522</v>
       </c>
       <c r="Y344" t="n">
-        <v>5.112923429673022</v>
+        <v>2.117026087797967</v>
       </c>
       <c r="Z344" t="n">
-        <v>4.870805340385229</v>
+        <v>2.037513738015424</v>
       </c>
       <c r="AA344" t="n">
-        <v>4.82345279305035</v>
+        <v>2.021963011021581</v>
       </c>
       <c r="AB344" t="n">
-        <v>5.948606939477194</v>
+        <v>2.391467207561101</v>
       </c>
       <c r="AC344" t="n">
-        <v>4.705101895108301</v>
+        <v>1.983096200111552</v>
       </c>
       <c r="AD344" t="n">
-        <v>4.953757426015597</v>
+        <v>2.064755466492776</v>
       </c>
       <c r="AE344" t="n">
-        <v>3.871744848604357</v>
+        <v>1.709419098287879</v>
       </c>
       <c r="AF344" t="n">
-        <v>5.831684600895031</v>
+        <v>2.353069540083693</v>
       </c>
       <c r="AG344" t="n">
-        <v>4.656304491779974</v>
+        <v>1.967070977818848</v>
       </c>
       <c r="AH344" t="n">
-        <v>5.061809025134025</v>
+        <v>2.100239954946075</v>
       </c>
       <c r="AI344" t="n">
-        <v>4.149877844187959</v>
+        <v>1.800758857724948</v>
       </c>
       <c r="AJ344" t="n">
-        <v>4.523496945283465</v>
+        <v>1.923456557591701</v>
       </c>
       <c r="AK344" t="n">
-        <v>5.140689265620868</v>
+        <v>2.126144476541179</v>
       </c>
       <c r="AL344" t="n">
-        <v>3.804643117672577</v>
+        <v>1.687382676653477</v>
       </c>
       <c r="AM344" t="n">
-        <v>6.143480966872097</v>
+        <v>2.455464457313631</v>
       </c>
       <c r="AN344" t="n">
-        <v>4.219068089870151</v>
+        <v>1.82348115423904</v>
       </c>
       <c r="AO344" t="n">
-        <v>4.491469382279539</v>
+        <v>1.912938604142862</v>
       </c>
       <c r="AP344" t="n">
-        <v>5.758194874770592</v>
+        <v>2.328935280532009</v>
       </c>
       <c r="AQ344" t="n">
-        <v>4.800571591694061</v>
+        <v>2.014448751797755</v>
       </c>
       <c r="AR344" t="n">
-        <v>4.297425082982418</v>
+        <v>1.849213839733865</v>
       </c>
       <c r="AS344" t="n">
-        <v>4.966511944992789</v>
+        <v>2.068944091048693</v>
       </c>
       <c r="AT344" t="n">
-        <v>4.672958850113672</v>
+        <v>1.972540322010057</v>
       </c>
       <c r="AU344" t="n">
-        <v>4.878666615304963</v>
+        <v>2.040095405675999</v>
       </c>
       <c r="AV344" t="n">
-        <v>4.156745069317739</v>
+        <v>1.803014076276197</v>
       </c>
       <c r="AW344" t="n">
-        <v>5.600669553733506</v>
+        <v>2.277203464612133</v>
       </c>
     </row>
     <row r="345">

--- a/xpts_schedule.xlsx
+++ b/xpts_schedule.xlsx
@@ -18229,127 +18229,127 @@
         <v>2390</v>
       </c>
       <c r="I114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114" t="b">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>85</v>
+        <v>16.24</v>
       </c>
       <c r="L114" t="n">
         <v>0.07346043236767437</v>
       </c>
       <c r="M114" t="n">
-        <v>3.662806026542352</v>
+        <v>1.102458853425694</v>
       </c>
       <c r="N114" t="n">
-        <v>124.53540490244</v>
+        <v>37.48360101647359</v>
       </c>
       <c r="O114" t="n">
-        <v>22.64280089135272</v>
+        <v>6.815200184813381</v>
       </c>
       <c r="P114" t="n">
-        <v>3.529937580737407</v>
+        <v>1.09311018294042</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.249768369117335</v>
+        <v>1.134316035680258</v>
       </c>
       <c r="R114" t="n">
-        <v>3.896503079502519</v>
+        <v>1.100157843241872</v>
       </c>
       <c r="S114" t="n">
-        <v>4.430955697680083</v>
+        <v>1.118857052995245</v>
       </c>
       <c r="T114" t="n">
-        <v>3.064576888060239</v>
+        <v>1.087431649296989</v>
       </c>
       <c r="U114" t="n">
-        <v>3.670097528605993</v>
+        <v>1.104378695837022</v>
       </c>
       <c r="V114" t="n">
-        <v>3.782180773894456</v>
+        <v>1.101944306236178</v>
       </c>
       <c r="W114" t="n">
-        <v>3.585933140350973</v>
+        <v>1.09691189033912</v>
       </c>
       <c r="X114" t="n">
-        <v>3.375993336452499</v>
+        <v>1.102918007914535</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.743610834779941</v>
+        <v>1.076532241083744</v>
       </c>
       <c r="Z114" t="n">
-        <v>4.249734455982431</v>
+        <v>1.124515913109744</v>
       </c>
       <c r="AA114" t="n">
-        <v>3.134394552579484</v>
+        <v>1.088939080792935</v>
       </c>
       <c r="AB114" t="n">
-        <v>4.158724670984309</v>
+        <v>1.120509104959202</v>
       </c>
       <c r="AC114" t="n">
-        <v>3.679756572165583</v>
+        <v>1.101711814095433</v>
       </c>
       <c r="AD114" t="n">
-        <v>3.909268773667836</v>
+        <v>1.102144265329832</v>
       </c>
       <c r="AE114" t="n">
-        <v>3.072695558576167</v>
+        <v>1.085366742005973</v>
       </c>
       <c r="AF114" t="n">
-        <v>3.474550319013446</v>
+        <v>1.087359827540332</v>
       </c>
       <c r="AG114" t="n">
-        <v>3.20092485314813</v>
+        <v>1.092295531050544</v>
       </c>
       <c r="AH114" t="n">
-        <v>3.589532099337092</v>
+        <v>1.097729479624574</v>
       </c>
       <c r="AI114" t="n">
-        <v>4.250974697507265</v>
+        <v>1.129359227237309</v>
       </c>
       <c r="AJ114" t="n">
-        <v>3.070922605619716</v>
+        <v>1.080000574069382</v>
       </c>
       <c r="AK114" t="n">
-        <v>3.587131863636517</v>
+        <v>1.106802668788919</v>
       </c>
       <c r="AL114" t="n">
-        <v>3.94629508588919</v>
+        <v>1.12741504820761</v>
       </c>
       <c r="AM114" t="n">
-        <v>3.152181434253956</v>
+        <v>1.083606821515018</v>
       </c>
       <c r="AN114" t="n">
-        <v>3.666694428980565</v>
+        <v>1.108809063623849</v>
       </c>
       <c r="AO114" t="n">
-        <v>3.662489906548942</v>
+        <v>1.108102812863336</v>
       </c>
       <c r="AP114" t="n">
-        <v>4.464672110324256</v>
+        <v>1.123741262594347</v>
       </c>
       <c r="AQ114" t="n">
-        <v>3.675229423856748</v>
+        <v>1.100739848620341</v>
       </c>
       <c r="AR114" t="n">
-        <v>3.868797708944506</v>
+        <v>1.096488270705945</v>
       </c>
       <c r="AS114" t="n">
-        <v>4.090726979764156</v>
+        <v>1.114360810305</v>
       </c>
       <c r="AT114" t="n">
-        <v>4.480780764846767</v>
+        <v>1.126385195023775</v>
       </c>
       <c r="AU114" t="n">
-        <v>3.246866936734529</v>
+        <v>1.083781495995543</v>
       </c>
       <c r="AV114" t="n">
-        <v>2.978519237572565</v>
+        <v>1.072823980477998</v>
       </c>
       <c r="AW114" t="n">
-        <v>3.593982633324352</v>
+        <v>1.104054272371274</v>
       </c>
     </row>
     <row r="115">
@@ -51848,7 +51848,7 @@
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr"/>
       <c r="H330" t="n">
-        <v>155</v>
+        <v>2003</v>
       </c>
       <c r="I330" t="b">
         <v>1</v>
@@ -51860,118 +51860,118 @@
         <v>80.76000000000001</v>
       </c>
       <c r="L330" t="n">
-        <v>0.1038342406192515</v>
+        <v>0.06915554533597452</v>
       </c>
       <c r="M330" t="n">
-        <v>4.275275536734638</v>
+        <v>3.904483851786841</v>
       </c>
       <c r="N330" t="n">
-        <v>145.3593682489777</v>
+        <v>132.7524509607526</v>
       </c>
       <c r="O330" t="n">
-        <v>29.07187364979554</v>
+        <v>26.55049019215052</v>
       </c>
       <c r="P330" t="n">
-        <v>3.907344618869979</v>
+        <v>3.571331926163603</v>
       </c>
       <c r="Q330" t="n">
-        <v>4.060885122626471</v>
+        <v>3.693272126018135</v>
       </c>
       <c r="R330" t="n">
-        <v>4.409895893321237</v>
+        <v>4.033340193985222</v>
       </c>
       <c r="S330" t="n">
-        <v>4.183201383281054</v>
+        <v>3.822520300386273</v>
       </c>
       <c r="T330" t="n">
-        <v>5.182240724395984</v>
+        <v>4.724489847015024</v>
       </c>
       <c r="U330" t="n">
-        <v>3.257096547904886</v>
+        <v>2.969529408066327</v>
       </c>
       <c r="V330" t="n">
-        <v>4.383479730536396</v>
+        <v>3.99349835086278</v>
       </c>
       <c r="W330" t="n">
-        <v>4.37135525422534</v>
+        <v>3.983221408169741</v>
       </c>
       <c r="X330" t="n">
-        <v>5.389978922875514</v>
+        <v>4.93187759723401</v>
       </c>
       <c r="Y330" t="n">
-        <v>4.311945005880044</v>
+        <v>3.938949389296695</v>
       </c>
       <c r="Z330" t="n">
-        <v>3.602872772153578</v>
+        <v>3.286096504969487</v>
       </c>
       <c r="AA330" t="n">
-        <v>4.430012185226841</v>
+        <v>4.064154687486242</v>
       </c>
       <c r="AB330" t="n">
-        <v>4.170307864438441</v>
+        <v>3.811729685167904</v>
       </c>
       <c r="AC330" t="n">
-        <v>4.498887864482682</v>
+        <v>4.123246170947161</v>
       </c>
       <c r="AD330" t="n">
-        <v>4.288598564055933</v>
+        <v>3.905764572929137</v>
       </c>
       <c r="AE330" t="n">
-        <v>3.374164926423676</v>
+        <v>3.09062059720207</v>
       </c>
       <c r="AF330" t="n">
-        <v>4.296403974564643</v>
+        <v>3.925915020170736</v>
       </c>
       <c r="AG330" t="n">
-        <v>4.989445659925866</v>
+        <v>4.556130205078243</v>
       </c>
       <c r="AH330" t="n">
-        <v>3.694870697113122</v>
+        <v>3.367785731151837</v>
       </c>
       <c r="AI330" t="n">
-        <v>4.262047228772539</v>
+        <v>3.885754802085987</v>
       </c>
       <c r="AJ330" t="n">
-        <v>4.859770717994261</v>
+        <v>4.416188092427795</v>
       </c>
       <c r="AK330" t="n">
-        <v>4.534004985365924</v>
+        <v>4.153134961202328</v>
       </c>
       <c r="AL330" t="n">
-        <v>3.622663252789836</v>
+        <v>3.300977180567902</v>
       </c>
       <c r="AM330" t="n">
-        <v>3.788639861279894</v>
+        <v>3.451638871637733</v>
       </c>
       <c r="AN330" t="n">
-        <v>5.343872089063066</v>
+        <v>4.892709761293085</v>
       </c>
       <c r="AO330" t="n">
-        <v>3.534349088102447</v>
+        <v>3.23086916522985</v>
       </c>
       <c r="AP330" t="n">
-        <v>3.720915692934248</v>
+        <v>3.403722896157801</v>
       </c>
       <c r="AQ330" t="n">
-        <v>5.254460290868907</v>
+        <v>4.816249689618381</v>
       </c>
       <c r="AR330" t="n">
-        <v>5.236503515820664</v>
+        <v>4.766754412259465</v>
       </c>
       <c r="AS330" t="n">
-        <v>3.337399214824336</v>
+        <v>3.0508536321415</v>
       </c>
       <c r="AT330" t="n">
-        <v>3.95789698871494</v>
+        <v>3.625828166920657</v>
       </c>
       <c r="AU330" t="n">
-        <v>4.334417887993344</v>
+        <v>3.955178114129279</v>
       </c>
       <c r="AV330" t="n">
-        <v>3.64254097023243</v>
+        <v>3.328173173993184</v>
       </c>
       <c r="AW330" t="n">
-        <v>5.126898751919172</v>
+        <v>4.68094431878703</v>
       </c>
     </row>
     <row r="331">
